--- a/output/2026-10-10_18_Serbia_Podunavski_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-10_18_Serbia_Podunavski_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -464,7 +464,6 @@
           <t>Woby Haus - prodaja mašina i alata</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Podunavski - Smederevo</t>
@@ -480,10 +479,9 @@
           <t>026/463-2144</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Catena di negozi di vendita macchine e utensili con piu' sedi in Serbia (Smederevo, Beograd, Novi Sad, Valjevo, Indjija, ecc.); sede Smederevo in Despota Djurdja 15. Rivenditore, non produttore. Nessun sito ufficiale o email generica reperiti. Fonte: planplus.rs (directory, molteplici schede confermano indirizzo e telefono).</t>
+          <t>Catena di negozi di vendita macchine e utensili con piu' sedi in Serbia (Smederevo, Beograd, Novi Sad, Valjevo, Indjija, ecc.); sede Smederevo in Despota Djurdja 15. Rivenditore, non produttore. Nessun sito ufficiale o email generica reperiti. Fonte: planplus.rs (directory, molteplici schede confermano indirizzo e telefono). [DUPLICATO — vedi anche: 2026-10-08_01_Serbia_Kolubarski_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
